--- a/astro-site/public/dl/pizza-shop-checklist-templates/BONUS-02-pizza-shop-holiday-calendar.xlsx
+++ b/astro-site/public/dl/pizza-shop-checklist-templates/BONUS-02-pizza-shop-holiday-calendar.xlsx
@@ -815,12 +815,12 @@
       </c>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t>Super Bowl Sunday (2nd Sunday in Feb)</t>
+          <t>Feb 9 — National Pizza Day + Super Bowl Sunday (2nd Sunday in Feb)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
         <is>
-          <t>Pre-orders and big party orders, dough balls cold-fermenting ahead, extra drivers and boxes, a short menu to push more orders per hour</t>
+          <t>National Pizza Day: a one-day deal and a social post. Super Bowl: pre-orders and big party orders, dough balls cold-fermenting ahead, extra drivers and boxes, a short menu to push more orders per hour</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -885,17 +885,17 @@
     <row r="9">
       <c r="A9" s="17" t="inlineStr">
         <is>
-          <t>March</t>
+          <t>February–April</t>
         </is>
       </c>
       <c r="B9" s="18" t="inlineStr">
         <is>
-          <t>Mar 17 — St. Patrick's Day + March Madness</t>
+          <t>Lent Fridays + Easter Sunday (varies)</t>
         </is>
       </c>
       <c r="C9" s="18" t="inlineStr">
         <is>
-          <t>Themed specials; March Madness games (mid-March to early April) lift delivery: extra drivers; beer only with a license, 21+ with ID</t>
+          <t>Meatless Fridays in Lent: cheese, veggie or marinara specials; Easter: decide hours, family orders</t>
         </is>
       </c>
       <c r="D9" s="17" t="inlineStr">
@@ -910,17 +910,17 @@
     <row r="10">
       <c r="A10" s="20" t="inlineStr">
         <is>
-          <t>March–April</t>
+          <t>March</t>
         </is>
       </c>
       <c r="B10" s="21" t="inlineStr">
         <is>
-          <t>Lent Fridays + Easter Sunday (varies)</t>
+          <t>Mar 14 — Pi Day + Mar 17 — St. Patrick's Day + March Madness</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr">
         <is>
-          <t>Meatless Fridays in Lent: cheese, veggie or marinara specials; Easter: decide hours, family orders</t>
+          <t>Pi Day: a $3.14 deal or a pie special. St. Patrick's: themed specials. March Madness games (mid-March to early April) lift delivery: extra drivers; beer only with a license, 21+ with ID</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -960,22 +960,22 @@
     <row r="12">
       <c r="A12" s="20" t="inlineStr">
         <is>
-          <t>May–June</t>
+          <t>April–June</t>
         </is>
       </c>
       <c r="B12" s="21" t="inlineStr">
         <is>
-          <t>Graduation season</t>
+          <t>NBA &amp; NHL playoffs (game nights)</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr">
         <is>
-          <t>Set group menu, deposit and price per person, private area; big carryout party orders for graduations</t>
+          <t>Game nights = delivery peak: extra drivers and dough, game-night deals, screens if you have a dining room</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
         <is>
-          <t>1 month</t>
+          <t>1 week</t>
         </is>
       </c>
       <c r="E12" s="19" t="n"/>
@@ -985,22 +985,22 @@
     <row r="13">
       <c r="A13" s="17" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>May–June</t>
         </is>
       </c>
       <c r="B13" s="18" t="inlineStr">
         <is>
-          <t>NBA &amp; NHL playoffs (game nights)</t>
+          <t>Graduation season</t>
         </is>
       </c>
       <c r="C13" s="18" t="inlineStr">
         <is>
-          <t>Game nights = delivery peak: extra drivers and dough, game-night deals, screens if you have a dining room</t>
+          <t>Set group menu, deposit and price per person, private area; big carryout party orders for graduations</t>
         </is>
       </c>
       <c r="D13" s="17" t="inlineStr">
         <is>
-          <t>1 week</t>
+          <t>1 month</t>
         </is>
       </c>
       <c r="E13" s="19" t="n"/>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="C18" s="21" t="inlineStr">
         <is>
-          <t>Holiday service, extra staff, longer hours, summer menu; more drivers and the patio at full capacity</t>
+          <t>Summer hours and menu, staff vacations; extra staff and drivers where summer is busy (beach and tourist areas); patio at full capacity</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="C19" s="18" t="inlineStr">
         <is>
-          <t>Fall menu, lunch specials for the back-to-routine crowd and game-day deals for football: Sunday and Monday night delivery peak</t>
+          <t>Fall menu, back-to-school lunch specials and game-day deals for football: Thursday, Sunday and Monday night games and college Saturdays lift delivery</t>
         </is>
       </c>
       <c r="D19" s="17" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B20" s="21" t="inlineStr">
         <is>
-          <t>Oct 31 — Halloween</t>
+          <t>National Pizza Month + Oct 31 — Halloween</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
         <is>
-          <t>Big delivery night: extra dough, boxes and drivers; themed decor and special pizzas (no cocktails)</t>
+          <t>National Pizza Month: a pizza of the week or a loyalty push all month. Halloween: big delivery night: extra dough, boxes and drivers; themed decor and special pizzas</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="C26" s="21" t="inlineStr">
         <is>
-          <t>Big delivery night: extra dough and drivers, closing hours; if the dining room is open, party favors and a midnight toast (alcohol only if your license allows; 21+ with ID); night shifts</t>
+          <t>Big delivery night: extra dough and drivers, closing hours; if the dining room is open, party favors and a midnight toast (alcohol only if your license allows and, if it's free, only where your state allows giving alcohol away; 21+ with ID); night shifts</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
